--- a/site/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/headings.xlsx
+++ b/site/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Operation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -683,29 +683,29 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>Rollout Configuration</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KFDNVV411T92KRVN0G17H9D2</t>
+          <t>h_01KVSY2BB8HRF8T4EV2TC3A7RB</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KFDNVV411T92KRVN0G17H9D2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KVSY2BB8HRF8T4EV2TC3A7RB</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Control how data sync runs from source</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KFDPQC99R8SX4J34G4REV4M3</t>
+          <t>h_01KVSVZEP2S8PBK1P132D468YK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KFDPQC99R8SX4J34G4REV4M3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KVSVZEP2S8PBK1P132D468YK</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Email Notification - Success</t>
+          <t>Exceptions handling</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,164 +737,230 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KFDPWRK3JBR0HV1SHVH6ZA32</t>
+          <t>h_01KTNYZGQBQF9DVJBEWP0WMZEM</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KFDPWRK3JBR0HV1SHVH6ZA32</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KTNYZGQBQF9DVJBEWP0WMZEM</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Email Notification - Failure</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KFDPX0TC9016VNCP6C29YPND</t>
+          <t>h_01KFDNVV411T92KRVN0G17H9D2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KFDPX0TC9016VNCP6C29YPND</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KFDNVV411T92KRVN0G17H9D2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KS046J3X6JRK084CGHDBBTKX</t>
+          <t>h_01KFDPQC99R8SX4J34G4REV4M3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KS046J3X6JRK084CGHDBBTKX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KFDPQC99R8SX4J34G4REV4M3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rollout Configuration</t>
+          <t>Email Notification - Success</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KS04S2MMRM5F25FZBP1NPHMJ</t>
+          <t>h_01KFDPWRK3JBR0HV1SHVH6ZA32</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KS04S2MMRM5F25FZBP1NPHMJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KFDPWRK3JBR0HV1SHVH6ZA32</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Email Notification - Failure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KS047SF85TRPX12M6NVQY121</t>
+          <t>h_01KFDPX0TC9016VNCP6C29YPND</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KS047SF85TRPX12M6NVQY121</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KFDPX0TC9016VNCP6C29YPND</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KS046J3X6JRK084CGHDBBTKX</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KS046J3X6JRK084CGHDBBTKX</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Rollout Configuration</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KS04S2MMRM5F25FZBP1NPHMJ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KS04S2MMRM5F25FZBP1NPHMJ</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01KS047SF85TRPX12M6NVQY121</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KS047SF85TRPX12M6NVQY121</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/headings.xlsx
+++ b/site/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,12 +693,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KVSY2BB8HRF8T4EV2TC3A7RB</t>
+          <t>h_01KVT112D3DMRDCTW0VCBA5RYW</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KVSY2BB8HRF8T4EV2TC3A7RB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KVT112D3DMRDCTW0VCBA5RYW</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KFDNVV411T92KRVN0G17H9D2</t>
+          <t>h_01KTNYTN68HDHWE6C6PFJ258ZN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KFDNVV411T92KRVN0G17H9D2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KTNYTN68HDHWE6C6PFJ258ZN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Notification settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KFDPQC99R8SX4J34G4REV4M3</t>
+          <t>h_01KTNZK355YJVK16C1J30AK4BG</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KFDPQC99R8SX4J34G4REV4M3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KTNZK355YJVK16C1J30AK4BG</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Email Notification - Success</t>
+          <t>Operational settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,107 +803,107 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KFDPWRK3JBR0HV1SHVH6ZA32</t>
+          <t>h_01KTNZK3564RP9AQ86H2HTMMC0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KFDPWRK3JBR0HV1SHVH6ZA32</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KTNZK3564RP9AQ86H2HTMMC0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Email Notification - Failure</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KFDPX0TC9016VNCP6C29YPND</t>
+          <t>h_01KS046J3X6JRK084CGHDBBTKX</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KFDPX0TC9016VNCP6C29YPND</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KS046J3X6JRK084CGHDBBTKX</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Rollout Configuration</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KS046J3X6JRK084CGHDBBTKX</t>
+          <t>h_01KS04S2MMRM5F25FZBP1NPHMJ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KS046J3X6JRK084CGHDBBTKX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KS04S2MMRM5F25FZBP1NPHMJ</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rollout Configuration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KS04S2MMRM5F25FZBP1NPHMJ</t>
+          <t>h_01KS047SF85TRPX12M6NVQY121</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KS04S2MMRM5F25FZBP1NPHMJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KS047SF85TRPX12M6NVQY121</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KS047SF85TRPX12M6NVQY121</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KS047SF85TRPX12M6NVQY121</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,19 +913,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,32 +935,10 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Update the Integration to the Latest Version</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/headings.xlsx
+++ b/site/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,12 +693,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KVT112D3DMRDCTW0VCBA5RYW</t>
+          <t>h_01KVW1WFVD7FMJK7Z2ZSWFG9WB</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KVT112D3DMRDCTW0VCBA5RYW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KVW1WFVD7FMJK7Z2ZSWFG9WB</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,63 +825,63 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KS046J3X6JRK084CGHDBBTKX</t>
+          <t>h_01KS047SF85TRPX12M6NVQY121</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KS046J3X6JRK084CGHDBBTKX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KS047SF85TRPX12M6NVQY121</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rollout Configuration</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KS04S2MMRM5F25FZBP1NPHMJ</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KS04S2MMRM5F25FZBP1NPHMJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KS047SF85TRPX12M6NVQY121</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KS047SF85TRPX12M6NVQY121</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,54 +891,10 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Update the Integration to the Latest Version</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-WorkforceNow-Cloud-Storage-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
